--- a/Result/profitability/5706.xlsx
+++ b/Result/profitability/5706.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>0.82625</v>
+        <v>0.805</v>
       </c>
       <c r="N2" t="n">
-        <v>15.16125</v>
+        <v>14.68</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.76</v>
+        <v>0.8187500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>15.305</v>
+        <v>15.065</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7525000000000001</v>
+        <v>0.83375</v>
       </c>
       <c r="N4" t="n">
-        <v>15.235</v>
+        <v>14.855</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0.745</v>
+        <v>0.7887500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>15.4375</v>
+        <v>15.24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7712500000000001</v>
+        <v>0.74625</v>
       </c>
       <c r="N6" t="n">
-        <v>16.39</v>
+        <v>15.93125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.61875</v>
+        <v>0.6775</v>
       </c>
       <c r="N7" t="n">
-        <v>16.585</v>
+        <v>16.175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58875</v>
+        <v>0.6575</v>
       </c>
       <c r="N8" t="n">
-        <v>16.5575</v>
+        <v>16.19875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>817</v>
+      </c>
+      <c r="D75" t="n">
+        <v>718</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>27</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>96</v>
+      </c>
+      <c r="J75" t="n">
+        <v>124</v>
+      </c>
+      <c r="K75" t="n">
+        <v>98</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.61625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8870967741935483</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1918449197860963</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4268292682926829</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1155815654718362</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
